--- a/artfynd/A 14855-2026 artfynd.xlsx
+++ b/artfynd/A 14855-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,6 +1128,117 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132697056</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106237</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Larslundsmalmen, Larslundsmalmen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>607802</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6515410</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14855-2026 artfynd.xlsx
+++ b/artfynd/A 14855-2026 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>132697056</v>
       </c>
       <c r="B6" t="n">
-        <v>106237</v>
+        <v>106241</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14855-2026 artfynd.xlsx
+++ b/artfynd/A 14855-2026 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>132697056</v>
       </c>
       <c r="B6" t="n">
-        <v>106241</v>
+        <v>106242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14855-2026 artfynd.xlsx
+++ b/artfynd/A 14855-2026 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>132697056</v>
       </c>
       <c r="B6" t="n">
-        <v>106242</v>
+        <v>106243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14855-2026 artfynd.xlsx
+++ b/artfynd/A 14855-2026 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>132697056</v>
       </c>
       <c r="B6" t="n">
-        <v>106243</v>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14855-2026 artfynd.xlsx
+++ b/artfynd/A 14855-2026 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>132697056</v>
       </c>
       <c r="B6" t="n">
-        <v>106244</v>
+        <v>106245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14855-2026 artfynd.xlsx
+++ b/artfynd/A 14855-2026 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>132697056</v>
       </c>
       <c r="B6" t="n">
-        <v>106245</v>
+        <v>106247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14855-2026 artfynd.xlsx
+++ b/artfynd/A 14855-2026 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>132697056</v>
       </c>
       <c r="B6" t="n">
-        <v>106247</v>
+        <v>106248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 14855-2026 artfynd.xlsx
+++ b/artfynd/A 14855-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>103694868</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607783.1427865373</v>
+        <v>607784</v>
       </c>
       <c r="R2" t="n">
-        <v>6515345.74546835</v>
+        <v>6515346</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,16 +780,11 @@
         <v>103694960</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -833,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607749.5487747953</v>
+        <v>607750</v>
       </c>
       <c r="R3" t="n">
-        <v>6515338.58358587</v>
+        <v>6515338</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,19 +846,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,41 +879,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103694908</v>
+        <v>123697634</v>
       </c>
       <c r="B4" t="n">
-        <v>92944</v>
+        <v>58790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6331648</v>
+        <v>208245</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Larslundsmalmen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607772</v>
+        <v>607726</v>
       </c>
       <c r="R4" t="n">
-        <v>6515323</v>
+        <v>6515186</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,12 +961,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hade gått över bilvägen i riktning mot Larslundsmalmen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,37 +980,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Anton Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Lst D inventering sandbarrskogar</t>
-        </is>
-      </c>
+          <t>Anton Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123697634</v>
+        <v>132697056</v>
       </c>
       <c r="B5" t="n">
-        <v>58345</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,54 +1010,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Larslundsmalmen, Srm</t>
+          <t>Larslundsmalmen, Larslundsmalmen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607726</v>
+        <v>607802</v>
       </c>
       <c r="R5" t="n">
-        <v>6515186</v>
+        <v>6515410</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,17 +1068,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hade gått över bilvägen i riktning mot Larslundsmalmen.</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,71 +1092,62 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Johansson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Johansson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132697056</v>
+        <v>103694908</v>
       </c>
       <c r="B6" t="n">
-        <v>106258</v>
+        <v>93218</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>6331648</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon aquiloniniger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Larslundsmalmen, Larslundsmalmen, Srm</t>
+          <t>Larslundsmalmen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607802</v>
+        <v>607772</v>
       </c>
       <c r="R6" t="n">
-        <v>6515410</v>
+        <v>6515323</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,22 +1171,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,15 +1191,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14855-2026 artfynd.xlsx
+++ b/artfynd/A 14855-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103694868</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103694960</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123697634</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697056</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,8 +1229,20 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103694908</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>